--- a/Repository/Модуль 1 - БД/EXCEL/Product.xlsx
+++ b/Repository/Модуль 1 - БД/EXCEL/Product.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivank\Desktop\Uceba\Projects\MDK.04.02\MDK.04.02.Demo.1\Repository\Модуль 1 - БД\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCDE8AA-4D9E-43DC-A0ED-F2140F3A422E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E161B2-E8B5-428E-B7BF-DDCDA63883EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -306,9 +306,6 @@
     <t>Нож строительный</t>
   </si>
   <si>
-    <t>SKU</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -324,9 +321,6 @@
     <t>ManufacturerId</t>
   </si>
   <si>
-    <t>ProductCategoryId</t>
-  </si>
-  <si>
     <t>CurrentDiscount</t>
   </si>
   <si>
@@ -340,6 +334,12 @@
   </si>
   <si>
     <t>Id</t>
+  </si>
+  <si>
+    <t>CategoryId</t>
+  </si>
+  <si>
+    <t>Sku</t>
   </si>
 </sst>
 </file>
@@ -765,40 +765,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="30">
       <c r="A1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="77.5">
